--- a/docs/AIPaddle-项目进度管控.xlsx
+++ b/docs/AIPaddle-项目进度管控.xlsx
@@ -3756,39 +3756,39 @@
       </c>
       <c r="H30" s="48" t="inlineStr">
         <is>
+          <t>进行中</t>
+        </is>
+      </c>
+      <c r="I30" s="47" t="inlineStr">
+        <is>
+          <t>Claude Code</t>
+        </is>
+      </c>
+      <c r="J30" s="47" t="inlineStr">
+        <is>
+          <t>2.4,SUP</t>
+        </is>
+      </c>
+      <c r="K30" s="48" t="inlineStr">
+        <is>
+          <t>迁移可重放/seed 与 test-data 一致</t>
+        </is>
+      </c>
+      <c r="L30" s="47" t="inlineStr">
+        <is>
+          <t>L3</t>
+        </is>
+      </c>
+      <c r="M30" s="48" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="N30" s="48" t="inlineStr">
+        <is>
           <t>未开始</t>
         </is>
       </c>
-      <c r="I30" s="47" t="inlineStr">
-        <is>
-          <t>Claude Code</t>
-        </is>
-      </c>
-      <c r="J30" s="47" t="inlineStr">
-        <is>
-          <t>2.4,SUP</t>
-        </is>
-      </c>
-      <c r="K30" s="48" t="inlineStr">
-        <is>
-          <t>迁移可重放/seed 与 test-data 一致</t>
-        </is>
-      </c>
-      <c r="L30" s="47" t="inlineStr">
-        <is>
-          <t>L3</t>
-        </is>
-      </c>
-      <c r="M30" s="48" t="inlineStr">
-        <is>
-          <t>已完成</t>
-        </is>
-      </c>
-      <c r="N30" s="48" t="inlineStr">
-        <is>
-          <t>未开始</t>
-        </is>
-      </c>
       <c r="O30" s="47" t="inlineStr">
         <is>
           <t>S0-DB×3</t>
@@ -3796,7 +3796,7 @@
       </c>
       <c r="P30" s="47" t="inlineStr">
         <is>
-          <t>seed=测试数据契约</t>
+          <t>seed=测试数据契约 | PR#51 CI 绿灯，待 S0-AUTH 人工验收</t>
         </is>
       </c>
       <c r="Q30" s="51" t="inlineStr">
@@ -3843,45 +3843,49 @@
       </c>
       <c r="H31" s="46" t="inlineStr">
         <is>
+          <t>进行中</t>
+        </is>
+      </c>
+      <c r="I31" s="45" t="inlineStr">
+        <is>
+          <t>Claude Code</t>
+        </is>
+      </c>
+      <c r="J31" s="45" t="inlineStr">
+        <is>
+          <t>3.1</t>
+        </is>
+      </c>
+      <c r="K31" s="45" t="inlineStr">
+        <is>
+          <t>S0-AUTH 全绿</t>
+        </is>
+      </c>
+      <c r="L31" s="45" t="inlineStr">
+        <is>
+          <t>L3/L4</t>
+        </is>
+      </c>
+      <c r="M31" s="46" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="N31" s="46" t="inlineStr">
+        <is>
           <t>未开始</t>
         </is>
       </c>
-      <c r="I31" s="45" t="inlineStr">
-        <is>
-          <t>Claude Code</t>
-        </is>
-      </c>
-      <c r="J31" s="45" t="inlineStr">
-        <is>
-          <t>3.1</t>
-        </is>
-      </c>
-      <c r="K31" s="45" t="inlineStr">
-        <is>
-          <t>S0-AUTH 全绿</t>
-        </is>
-      </c>
-      <c r="L31" s="45" t="inlineStr">
-        <is>
-          <t>L3/L4</t>
-        </is>
-      </c>
-      <c r="M31" s="46" t="inlineStr">
-        <is>
-          <t>已完成</t>
-        </is>
-      </c>
-      <c r="N31" s="46" t="inlineStr">
-        <is>
-          <t>未开始</t>
-        </is>
-      </c>
       <c r="O31" s="45" t="inlineStr">
         <is>
           <t>S0-AUTH×6</t>
         </is>
       </c>
-      <c r="P31" s="46" t="n"/>
+      <c r="P31" s="46" t="inlineStr">
+        <is>
+          <t>PR#51 CI 绿灯，待 S0-AUTH 人工验收</t>
+        </is>
+      </c>
       <c r="Q31" s="45" t="inlineStr">
         <is>
           <t>—</t>

--- a/docs/AIPaddle-项目进度管控.xlsx
+++ b/docs/AIPaddle-项目进度管控.xlsx
@@ -3412,7 +3412,7 @@
       </c>
       <c r="H26" s="42" t="inlineStr">
         <is>
-          <t>进行中</t>
+          <t>已完成</t>
         </is>
       </c>
       <c r="I26" s="41" t="inlineStr">
@@ -3452,7 +3452,7 @@
       </c>
       <c r="P26" s="42" t="inlineStr">
         <is>
-          <t>ADR-002 起草完成(2026-07-19)，待Perry拍板；认证=SupabaseAuth+服务端会话；上下文=org_id进JWT claim，契约{userId,orgId,roles}；RLS=请求级客户端生效/service_role单文件封装禁绕过</t>
+          <t>ADR-002 已拍板(2026-07-20)；认证=SupabaseAuth+服务端会话；上下文=org_id进JWT claim，契约{userId,orgId,roles}；RLS=请求级客户端生效/service_role锁死lib/db/admin.ts单文件，四道约束禁绕过；含3张时序图+current_org_id()改法(A道随3.3落地)</t>
         </is>
       </c>
       <c r="Q26" s="41" t="inlineStr">

--- a/docs/AIPaddle-项目进度管控.xlsx
+++ b/docs/AIPaddle-项目进度管控.xlsx
@@ -3534,12 +3534,12 @@
       </c>
       <c r="O27" s="45" t="inlineStr">
         <is>
-          <t>test-data ROLE_MATRIX</t>
+          <t>docs/adr/ADR-007-rbac-permission-model.md; test-data ROLE_MATRIX; TC-S0权限组</t>
         </is>
       </c>
       <c r="P27" s="46" t="inlineStr">
         <is>
-          <t>用例先行</t>
+          <t>ADR-007起草完成(2026-07-20)待拍板；RBAC+按action鉴权+默认拒绝+多角色并集；4角色x全模块矩阵(兼容ROLE_MATRIX 11条)；API入口requirePermission()落地3.4；平台超管暂缓阶段6；3待拍板点</t>
         </is>
       </c>
       <c r="Q27" s="45" t="inlineStr">
@@ -3621,10 +3621,14 @@
       </c>
       <c r="O28" s="47" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="P28" s="48" t="n"/>
+          <t>docs/adr/ADR-008-data-access-layer.md</t>
+        </is>
+      </c>
+      <c r="P28" s="48" t="inlineStr">
+        <is>
+          <t>ADR-008起草完成(2026-07-20)待拍板；四层单向依赖(组件-&gt;API-&gt;lib/data-&gt;supabase)；组件禁直连mock/supabase；lib/data唯一碰库+ctx+server-only；Repository逐页切配合3.5；铁律入CLAUDE.md</t>
+        </is>
+      </c>
       <c r="Q28" s="47" t="inlineStr">
         <is>
           <t>—</t>

--- a/docs/AIPaddle-项目进度管控.xlsx
+++ b/docs/AIPaddle-项目进度管控.xlsx
@@ -3499,7 +3499,7 @@
       </c>
       <c r="H27" s="46" t="inlineStr">
         <is>
-          <t>未开始</t>
+          <t>已完成</t>
         </is>
       </c>
       <c r="I27" s="45" t="inlineStr">
@@ -3539,7 +3539,7 @@
       </c>
       <c r="P27" s="46" t="inlineStr">
         <is>
-          <t>ADR-007起草完成(2026-07-20)待拍板；RBAC+按action鉴权+默认拒绝+多角色并集；4角色x全模块矩阵(兼容ROLE_MATRIX 11条)；API入口requirePermission()落地3.4；平台超管暂缓阶段6；3待拍板点</t>
+          <t>ADR-007已拍板(2026-07-20)；RBAC+按action鉴权+默认拒绝+多角色并集；4角色x全模块矩阵；按PRD补齐统一上架审核：Agent/Skill/Workflow三资产共用draft-&gt;pending-&gt;published，部门级Admin/Auditor单审，企业级仅Admin创建+Admin必审+可指派AIBP协同双签；requirePermission()落地3.4；平台超管暂缓阶段6</t>
         </is>
       </c>
       <c r="Q27" s="45" t="inlineStr">
@@ -3586,7 +3586,7 @@
       </c>
       <c r="H28" s="48" t="inlineStr">
         <is>
-          <t>未开始</t>
+          <t>已完成</t>
         </is>
       </c>
       <c r="I28" s="47" t="inlineStr">
@@ -3626,7 +3626,7 @@
       </c>
       <c r="P28" s="48" t="inlineStr">
         <is>
-          <t>ADR-008起草完成(2026-07-20)待拍板；四层单向依赖(组件-&gt;API-&gt;lib/data-&gt;supabase)；组件禁直连mock/supabase；lib/data唯一碰库+ctx+server-only；Repository逐页切配合3.5；铁律入CLAUDE.md</t>
+          <t>ADR-008已拍板(2026-07-20)；四层单向依赖(组件-&gt;API-&gt;lib/data-&gt;supabase)；组件禁直连mock/supabase；lib/data唯一碰库+ctx+server-only；Repository逐页切配合3.5；铁律入CLAUDE.md</t>
         </is>
       </c>
       <c r="Q28" s="47" t="inlineStr">

--- a/docs/AIPaddle-项目进度管控.xlsx
+++ b/docs/AIPaddle-项目进度管控.xlsx
@@ -99,7 +99,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -121,11 +121,55 @@
         <color rgb="00D1D5DB"/>
       </bottom>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00D1D5DB"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00D1D5DB"/>
+      </right>
+      <top style="thin">
+        <color rgb="00D1D5DB"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00D1D5DB"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00D1D5DB"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00D1D5DB"/>
+      </right>
+      <top style="thin">
+        <color rgb="00D1D5DB"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00D1D5DB"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -187,6 +231,8 @@
     <xf numFmtId="0" fontId="5" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -760,6 +806,9 @@
           <t>3.1 Seed 脚本已执行，Supabase 两租户五账号数据已写入</t>
         </is>
       </c>
+      <c r="C13" s="21" t="n"/>
+      <c r="D13" s="21" t="n"/>
+      <c r="E13" s="22" t="n"/>
     </row>
     <row r="14" ht="20" customHeight="1">
       <c r="A14" s="7" t="inlineStr">
@@ -772,6 +821,9 @@
           <t>3.2 登录/注册/退出已实装，用户亲手验证登录成功</t>
         </is>
       </c>
+      <c r="C14" s="21" t="n"/>
+      <c r="D14" s="21" t="n"/>
+      <c r="E14" s="22" t="n"/>
     </row>
     <row r="15" ht="20" customHeight="1">
       <c r="A15" s="7" t="inlineStr">
@@ -784,6 +836,9 @@
           <t>原型迁入 public/prototype/，根路径跳转逻辑已配置</t>
         </is>
       </c>
+      <c r="C15" s="21" t="n"/>
+      <c r="D15" s="21" t="n"/>
+      <c r="E15" s="22" t="n"/>
     </row>
     <row r="16" ht="20" customHeight="1">
       <c r="A16" s="9" t="inlineStr">
@@ -796,6 +851,9 @@
           <t>0.7 服务器部署（aipaddle.net）：代码已部署，需亲手在线验证</t>
         </is>
       </c>
+      <c r="C16" s="21" t="n"/>
+      <c r="D16" s="21" t="n"/>
+      <c r="E16" s="22" t="n"/>
     </row>
     <row r="17" ht="20" customHeight="1">
       <c r="A17" s="11" t="inlineStr">
@@ -808,6 +866,9 @@
           <t>#49/#50 Issue 标签仍显示「未开始」，需关闭并回填状态</t>
         </is>
       </c>
+      <c r="C17" s="21" t="n"/>
+      <c r="D17" s="21" t="n"/>
+      <c r="E17" s="22" t="n"/>
     </row>
     <row r="18" ht="20" customHeight="1">
       <c r="A18" s="13" t="inlineStr">
@@ -820,6 +881,9 @@
           <t>[3.3] 租户上下文中间件 — 当前应执行任务</t>
         </is>
       </c>
+      <c r="C18" s="21" t="n"/>
+      <c r="D18" s="21" t="n"/>
+      <c r="E18" s="22" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="7">
@@ -2524,7 +2588,7 @@
       </c>
       <c r="O25" s="8" t="inlineStr">
         <is>
-          <t>默认Kimi 2.5</t>
+          <t>ADR-003已拍板；嵌入模型遗留结案→ADR-009(2026-07-20待拍板)：Kimi无embedding接口，选通义text-embedding-v3@1536维(OpenAI兼容/中文强/国内低延迟)，对齐pgvector vector(1536)；封装lib/llm/embedding.ts；建议migration给chunks补embedding_model/dim(交A道)；解锁4.2.2</t>
         </is>
       </c>
     </row>

--- a/docs/AIPaddle-项目进度管控.xlsx
+++ b/docs/AIPaddle-项目进度管控.xlsx
@@ -11,6 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="📋 任务清单" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="🚩 里程碑关口" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="📝 决策日志" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="⚠️ 问题台账" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -51,7 +52,7 @@
       <sz val="9"/>
     </font>
   </fonts>
-  <fills count="10">
+  <fills count="11">
     <fill>
       <patternFill/>
     </fill>
@@ -98,8 +99,13 @@
         <fgColor rgb="00F3F4F6"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FEF3C7"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -121,11 +127,55 @@
         <color rgb="00D1D5DB"/>
       </bottom>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00D1D5DB"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00D1D5DB"/>
+      </right>
+      <top style="thin">
+        <color rgb="00D1D5DB"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00D1D5DB"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00D1D5DB"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00D1D5DB"/>
+      </right>
+      <top style="thin">
+        <color rgb="00D1D5DB"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00D1D5DB"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -185,6 +235,14 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -565,7 +623,7 @@
     <row r="1" ht="36" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>AIPaddle 项目进度仪表盘  ·  2026-07-20</t>
+          <t>AIPaddle 项目进度仪表盘  ·  2026-07-20（本次更新）</t>
         </is>
       </c>
     </row>
@@ -760,6 +818,9 @@
           <t>3.1 Seed 脚本已执行，Supabase 两租户五账号数据已写入</t>
         </is>
       </c>
+      <c r="C13" s="21" t="n"/>
+      <c r="D13" s="21" t="n"/>
+      <c r="E13" s="22" t="n"/>
     </row>
     <row r="14" ht="20" customHeight="1">
       <c r="A14" s="7" t="inlineStr">
@@ -772,6 +833,9 @@
           <t>3.2 登录/注册/退出已实装，用户亲手验证登录成功</t>
         </is>
       </c>
+      <c r="C14" s="21" t="n"/>
+      <c r="D14" s="21" t="n"/>
+      <c r="E14" s="22" t="n"/>
     </row>
     <row r="15" ht="20" customHeight="1">
       <c r="A15" s="7" t="inlineStr">
@@ -784,6 +848,9 @@
           <t>原型迁入 public/prototype/，根路径跳转逻辑已配置</t>
         </is>
       </c>
+      <c r="C15" s="21" t="n"/>
+      <c r="D15" s="21" t="n"/>
+      <c r="E15" s="22" t="n"/>
     </row>
     <row r="16" ht="20" customHeight="1">
       <c r="A16" s="9" t="inlineStr">
@@ -796,6 +863,9 @@
           <t>0.7 服务器部署（aipaddle.net）：代码已部署，需亲手在线验证</t>
         </is>
       </c>
+      <c r="C16" s="21" t="n"/>
+      <c r="D16" s="21" t="n"/>
+      <c r="E16" s="22" t="n"/>
     </row>
     <row r="17" ht="20" customHeight="1">
       <c r="A17" s="11" t="inlineStr">
@@ -808,6 +878,9 @@
           <t>#49/#50 Issue 标签仍显示「未开始」，需关闭并回填状态</t>
         </is>
       </c>
+      <c r="C17" s="21" t="n"/>
+      <c r="D17" s="21" t="n"/>
+      <c r="E17" s="22" t="n"/>
     </row>
     <row r="18" ht="20" customHeight="1">
       <c r="A18" s="13" t="inlineStr">
@@ -820,6 +893,9 @@
           <t>[3.3] 租户上下文中间件 — 当前应执行任务</t>
         </is>
       </c>
+      <c r="C18" s="21" t="n"/>
+      <c r="D18" s="21" t="n"/>
+      <c r="E18" s="22" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="7">
@@ -1311,156 +1387,156 @@
       <c r="O7" s="8" t="inlineStr"/>
     </row>
     <row r="8" ht="20" customHeight="1">
-      <c r="A8" s="17" t="inlineStr">
+      <c r="A8" s="16" t="inlineStr">
         <is>
           <t>0.6</t>
         </is>
       </c>
-      <c r="B8" s="17" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="C8" s="10" t="inlineStr">
+      <c r="B8" s="16" t="inlineStr">
+        <is>
+          <t>D1前</t>
+        </is>
+      </c>
+      <c r="C8" s="8" t="inlineStr">
         <is>
           <t>阶段0 环境</t>
         </is>
       </c>
-      <c r="D8" s="10" t="inlineStr">
+      <c r="D8" s="8" t="inlineStr">
         <is>
           <t>infra</t>
         </is>
       </c>
-      <c r="E8" s="10" t="inlineStr">
+      <c r="E8" s="8" t="inlineStr">
         <is>
           <t>GitHub Issues 工作流（模板+标签+批量建卡）</t>
         </is>
       </c>
-      <c r="F8" s="17" t="inlineStr">
+      <c r="F8" s="16" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="G8" s="17" t="inlineStr">
-        <is>
-          <t>🔄 进行中</t>
-        </is>
-      </c>
-      <c r="H8" s="17" t="inlineStr">
+      <c r="G8" s="16" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+      <c r="H8" s="16" t="inlineStr">
         <is>
           <t>AI</t>
         </is>
       </c>
-      <c r="I8" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J8" s="10" t="inlineStr">
+      <c r="I8" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J8" s="8" t="inlineStr">
         <is>
           <t>模板已入库；标签部分建立</t>
         </is>
       </c>
-      <c r="K8" s="17" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L8" s="17" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M8" s="17" t="inlineStr">
+      <c r="K8" s="16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L8" s="16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M8" s="16" t="inlineStr">
         <is>
           <t>部分</t>
         </is>
       </c>
-      <c r="N8" s="17" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O8" s="10" t="inlineStr">
-        <is>
-          <t>标签体系已定义；批量建卡待做</t>
+      <c r="N8" s="16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O8" s="8" t="inlineStr">
+        <is>
+          <t>GitHub Issues工作流：标签+模板+全量Issue已按ROADMAP v2.0重建（2026-07-20）</t>
         </is>
       </c>
     </row>
     <row r="9" ht="20" customHeight="1">
-      <c r="A9" s="17" t="inlineStr">
+      <c r="A9" s="16" t="inlineStr">
         <is>
           <t>0.7</t>
         </is>
       </c>
-      <c r="B9" s="17" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="C9" s="10" t="inlineStr">
+      <c r="B9" s="16" t="inlineStr">
+        <is>
+          <t>D1</t>
+        </is>
+      </c>
+      <c r="C9" s="8" t="inlineStr">
         <is>
           <t>阶段0 环境</t>
         </is>
       </c>
-      <c r="D9" s="10" t="inlineStr">
+      <c r="D9" s="8" t="inlineStr">
         <is>
           <t>infra</t>
         </is>
       </c>
-      <c r="E9" s="10" t="inlineStr">
+      <c r="E9" s="8" t="inlineStr">
         <is>
           <t>服务器部署链路（43.173.99.218→aipaddle.net）</t>
         </is>
       </c>
-      <c r="F9" s="17" t="inlineStr">
+      <c r="F9" s="16" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
-      <c r="G9" s="17" t="inlineStr">
-        <is>
-          <t>🔄 进行中</t>
-        </is>
-      </c>
-      <c r="H9" s="17" t="inlineStr">
+      <c r="G9" s="16" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+      <c r="H9" s="16" t="inlineStr">
         <is>
           <t>AI+Perry</t>
         </is>
       </c>
-      <c r="I9" s="10" t="inlineStr">
+      <c r="I9" s="8" t="inlineStr">
         <is>
           <t>0.2</t>
         </is>
       </c>
-      <c r="J9" s="10" t="inlineStr">
+      <c r="J9" s="8" t="inlineStr">
         <is>
           <t>Issue#52；线上可访问</t>
         </is>
       </c>
-      <c r="K9" s="17" t="inlineStr">
+      <c r="K9" s="16" t="inlineStr">
         <is>
           <t>E2E冒烟</t>
         </is>
       </c>
-      <c r="L9" s="17" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M9" s="17" t="inlineStr">
+      <c r="L9" s="16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M9" s="16" t="inlineStr">
         <is>
           <t>待验收</t>
         </is>
       </c>
-      <c r="N9" s="17" t="inlineStr">
+      <c r="N9" s="16" t="inlineStr">
         <is>
           <t>P-GLB-01</t>
         </is>
       </c>
-      <c r="O9" s="10" t="inlineStr">
-        <is>
-          <t>代码已部署PM2，需用户亲手验证</t>
+      <c r="O9" s="8" t="inlineStr">
+        <is>
+          <t>隐私窗口登录验收通过（2026-07-20），Issue #52 关闭</t>
         </is>
       </c>
     </row>
@@ -1472,7 +1548,7 @@
       </c>
       <c r="B10" s="18" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>D2</t>
         </is>
       </c>
       <c r="C10" s="19" t="inlineStr">
@@ -1535,7 +1611,11 @@
           <t>—</t>
         </is>
       </c>
-      <c r="O10" s="19" t="inlineStr"/>
+      <c r="O10" s="19" t="inlineStr">
+        <is>
+          <t>依赖0.7验收完成后执行；需Perry先在GitHub配置SSH_PRIVATE_KEY和SERVER_HOST两个Secret</t>
+        </is>
+      </c>
     </row>
     <row r="11" ht="20" customHeight="1">
       <c r="A11" s="17" t="inlineStr">
@@ -1545,7 +1625,7 @@
       </c>
       <c r="B11" s="17" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>D1</t>
         </is>
       </c>
       <c r="C11" s="10" t="inlineStr">
@@ -1560,7 +1640,7 @@
       </c>
       <c r="E11" s="10" t="inlineStr">
         <is>
-          <t>测试基建：Playwright已装；Vitest+RTL待做</t>
+          <t>测试基建：Playwright+Vitest+RTL已装；仅剩 0.9c 分支保护</t>
         </is>
       </c>
       <c r="F11" s="17" t="inlineStr">
@@ -1600,7 +1680,7 @@
       </c>
       <c r="M11" s="17" t="inlineStr">
         <is>
-          <t>部分通过</t>
+          <t>冒烟6条+单元7条全绿</t>
         </is>
       </c>
       <c r="N11" s="17" t="inlineStr">
@@ -1610,7 +1690,7 @@
       </c>
       <c r="O11" s="10" t="inlineStr">
         <is>
-          <t>0.9a完成；0.9b/c待做</t>
+          <t>0.9a✅Playwright 6条冒烟绿；0.9b✅Vitest+RTL装好(vitest.config+setup+test脚本),单元样例7条绿,CI启用单元测试步骤；待0.9c开main分支保护</t>
         </is>
       </c>
     </row>
@@ -1841,79 +1921,79 @@
       <c r="O15" s="8" t="inlineStr"/>
     </row>
     <row r="16" ht="20" customHeight="1">
-      <c r="A16" s="17" t="inlineStr">
+      <c r="A16" s="16" t="inlineStr">
         <is>
           <t>1.4</t>
         </is>
       </c>
-      <c r="B16" s="17" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="C16" s="10" t="inlineStr">
+      <c r="B16" s="16" t="inlineStr">
+        <is>
+          <t>D1</t>
+        </is>
+      </c>
+      <c r="C16" s="8" t="inlineStr">
         <is>
           <t>阶段1 产品</t>
         </is>
       </c>
-      <c r="D16" s="10" t="inlineStr">
+      <c r="D16" s="8" t="inlineStr">
         <is>
           <t>docs</t>
         </is>
       </c>
-      <c r="E16" s="10" t="inlineStr">
+      <c r="E16" s="8" t="inlineStr">
         <is>
           <t>MVP首个闭环场景确认</t>
         </is>
       </c>
-      <c r="F16" s="17" t="inlineStr">
+      <c r="F16" s="16" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
-      <c r="G16" s="17" t="inlineStr">
-        <is>
-          <t>🔄 进行中</t>
-        </is>
-      </c>
-      <c r="H16" s="17" t="inlineStr">
+      <c r="G16" s="16" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+      <c r="H16" s="16" t="inlineStr">
         <is>
           <t>Perry</t>
         </is>
       </c>
-      <c r="I16" s="10" t="inlineStr">
+      <c r="I16" s="8" t="inlineStr">
         <is>
           <t>1.3</t>
         </is>
       </c>
-      <c r="J16" s="10" t="inlineStr">
+      <c r="J16" s="8" t="inlineStr">
         <is>
           <t>确认 Agent 管理为第一条闭环</t>
         </is>
       </c>
-      <c r="K16" s="17" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L16" s="17" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M16" s="17" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N16" s="17" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O16" s="10" t="inlineStr">
-        <is>
-          <t>建议 Agent 管理；待用户拍板</t>
+      <c r="K16" s="16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L16" s="16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M16" s="16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N16" s="16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O16" s="8" t="inlineStr">
+        <is>
+          <t>MVP首个闭环=Agent管理（切片1），2026-07-20拍板，检测关口1放行</t>
         </is>
       </c>
     </row>
@@ -2839,7 +2919,7 @@
       </c>
       <c r="O30" s="20" t="inlineStr">
         <is>
-          <t>⭐ 当前应执行任务</t>
+          <t>下一个待执行任务；依赖3.1/3.2</t>
         </is>
       </c>
     </row>
@@ -2914,7 +2994,11 @@
           <t>S0-PERM-01~06</t>
         </is>
       </c>
-      <c r="O31" s="19" t="inlineStr"/>
+      <c r="O31" s="19" t="inlineStr">
+        <is>
+          <t>依赖3.3</t>
+        </is>
+      </c>
     </row>
     <row r="32" ht="20" customHeight="1">
       <c r="A32" s="18" t="inlineStr">
@@ -2987,7 +3071,11 @@
           <t>—</t>
         </is>
       </c>
-      <c r="O32" s="19" t="inlineStr"/>
+      <c r="O32" s="19" t="inlineStr">
+        <is>
+          <t>依赖3.3/3.4</t>
+        </is>
+      </c>
     </row>
     <row r="33" ht="20" customHeight="1">
       <c r="A33" s="18" t="inlineStr">
@@ -3060,7 +3148,11 @@
           <t>—</t>
         </is>
       </c>
-      <c r="O33" s="19" t="inlineStr"/>
+      <c r="O33" s="19" t="inlineStr">
+        <is>
+          <t>依赖0.7验收</t>
+        </is>
+      </c>
     </row>
     <row r="34" ht="20" customHeight="1">
       <c r="A34" s="18" t="inlineStr">
@@ -3133,7 +3225,11 @@
           <t>S0-ISO-*</t>
         </is>
       </c>
-      <c r="O34" s="19" t="inlineStr"/>
+      <c r="O34" s="19" t="inlineStr">
+        <is>
+          <t>检测关口3硬闸，必须全绿</t>
+        </is>
+      </c>
     </row>
     <row r="35" ht="20" customHeight="1">
       <c r="A35" s="15" t="inlineStr">
@@ -4123,12 +4219,12 @@
       </c>
       <c r="D2" s="17" t="inlineStr">
         <is>
-          <t>🔄 进行中</t>
+          <t>✅ 通过</t>
         </is>
       </c>
       <c r="E2" s="10" t="inlineStr">
         <is>
-          <t>Agent管理建议；待Perry拍板</t>
+          <t>Agent管理作为MVP首个闭环，2026-07-20拍板</t>
         </is>
       </c>
     </row>
@@ -4182,7 +4278,7 @@
       </c>
       <c r="E4" s="19" t="inlineStr">
         <is>
-          <t>当前进行3.3</t>
+          <t>0.7已验收；下一步3.3租户中间件</t>
         </is>
       </c>
     </row>
@@ -4527,4 +4623,126 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>任务</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>问题描述</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>解决方案</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>状态</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>负责方</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>0.7 服务器部署</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>服务器无git pull能力（HTTPS无凭证），每次部署需手动rsync</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>等0.8 GitHub Actions上线后自动化解决</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>⚠️ 遗留</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>AI（0.8完成后自动解决）</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>0.9a Playwright</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>CI中测试步骤仍被注释，自动化测试未在CI运行</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>0.9c：启用ci.yml测试步骤+开main分支保护</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>⬜ 待处理</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>AI</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>会话管理</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Supabase JWT Expiry仍为3600s（默认1h），24h硬限制可能被refresh token绕过</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>前往Supabase Dashboard→Auth→Configuration，将JWT expiry改为86400</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>⚠️ 需Perry操作</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Perry</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/docs/AIPaddle-项目进度管控.xlsx
+++ b/docs/AIPaddle-项目进度管控.xlsx
@@ -2588,7 +2588,7 @@
       </c>
       <c r="O25" s="8" t="inlineStr">
         <is>
-          <t>ADR-003已拍板；嵌入模型遗留结案→ADR-009(2026-07-20待拍板)：Kimi无embedding接口，选通义text-embedding-v3@1536维(OpenAI兼容/中文强/国内低延迟)，对齐pgvector vector(1536)；封装lib/llm/embedding.ts；建议migration给chunks补embedding_model/dim(交A道)；解锁4.2.2</t>
+          <t>ADR-003已拍板并2026-07-20修订：默认LLM Kimi→通义Qwen(qwen-plus)；嵌入=通义text-embedding-v3@1536维(ADR-009)，与对话同供应商同一把DASHSCOPE_API_KEY一家全包；换模因Kimi/DeepSeek无embedding接口；Key存.env.local(gitignore)+服务器环境变量；解锁4.2.2</t>
         </is>
       </c>
     </row>

--- a/docs/AIPaddle-项目进度管控.xlsx
+++ b/docs/AIPaddle-项目进度管控.xlsx
@@ -1184,7 +1184,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O38"/>
+  <dimension ref="A1:O42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -4063,6 +4063,314 @@
       <c r="O38" s="16" t="inlineStr">
         <is>
           <t>Issue #67</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="15" t="inlineStr">
+        <is>
+          <t>BUG-72</t>
+        </is>
+      </c>
+      <c r="B39" s="15" t="inlineStr">
+        <is>
+          <t>D2</t>
+        </is>
+      </c>
+      <c r="C39" s="15" t="inlineStr">
+        <is>
+          <t>Phase 3</t>
+        </is>
+      </c>
+      <c r="D39" s="15" t="inlineStr">
+        <is>
+          <t>缺陷</t>
+        </is>
+      </c>
+      <c r="E39" s="16" t="inlineStr">
+        <is>
+          <t>登录按钮偶发卡「登录中...」不跳转（会话已建立）</t>
+        </is>
+      </c>
+      <c r="F39" s="15" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="G39" s="22" t="inlineStr">
+        <is>
+          <t>⬜ 未开始</t>
+        </is>
+      </c>
+      <c r="H39" s="15" t="inlineStr">
+        <is>
+          <t>认证agent</t>
+        </is>
+      </c>
+      <c r="I39" s="15" t="inlineStr">
+        <is>
+          <t>3.2</t>
+        </is>
+      </c>
+      <c r="J39" s="16" t="inlineStr">
+        <is>
+          <t>连续5次登录均3s内跳转、loading态正确复位</t>
+        </is>
+      </c>
+      <c r="K39" s="15" t="inlineStr">
+        <is>
+          <t>L4</t>
+        </is>
+      </c>
+      <c r="L39" s="15" t="inlineStr">
+        <is>
+          <t>未写</t>
+        </is>
+      </c>
+      <c r="M39" s="15" t="inlineStr">
+        <is>
+          <t>⬜</t>
+        </is>
+      </c>
+      <c r="N39" s="15" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O39" s="16" t="inlineStr">
+        <is>
+          <t>Issue #72｜线上验证2026-07-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="15" t="inlineStr">
+        <is>
+          <t>BUG-73</t>
+        </is>
+      </c>
+      <c r="B40" s="15" t="inlineStr">
+        <is>
+          <t>D2</t>
+        </is>
+      </c>
+      <c r="C40" s="15" t="inlineStr">
+        <is>
+          <t>Phase 3</t>
+        </is>
+      </c>
+      <c r="D40" s="15" t="inlineStr">
+        <is>
+          <t>缺陷</t>
+        </is>
+      </c>
+      <c r="E40" s="16" t="inlineStr">
+        <is>
+          <t>DashboardShell 侧边栏点二级菜单不切换视图（仅监控可见）</t>
+        </is>
+      </c>
+      <c r="F40" s="15" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="G40" s="22" t="inlineStr">
+        <is>
+          <t>⬜ 未开始</t>
+        </is>
+      </c>
+      <c r="H40" s="15" t="inlineStr">
+        <is>
+          <t>Claude</t>
+        </is>
+      </c>
+      <c r="I40" s="15" t="inlineStr">
+        <is>
+          <t>3.5</t>
+        </is>
+      </c>
+      <c r="J40" s="16" t="inlineStr">
+        <is>
+          <t>点任一二级菜单主区正确切换视图</t>
+        </is>
+      </c>
+      <c r="K40" s="15" t="inlineStr">
+        <is>
+          <t>L4</t>
+        </is>
+      </c>
+      <c r="L40" s="15" t="inlineStr">
+        <is>
+          <t>未写</t>
+        </is>
+      </c>
+      <c r="M40" s="15" t="inlineStr">
+        <is>
+          <t>⬜</t>
+        </is>
+      </c>
+      <c r="N40" s="15" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O40" s="16" t="inlineStr">
+        <is>
+          <t>Issue #73｜二三级页无法使用直接原因</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="15" t="inlineStr">
+        <is>
+          <t>BUG-74</t>
+        </is>
+      </c>
+      <c r="B41" s="15" t="inlineStr">
+        <is>
+          <t>D2</t>
+        </is>
+      </c>
+      <c r="C41" s="15" t="inlineStr">
+        <is>
+          <t>Phase 3</t>
+        </is>
+      </c>
+      <c r="D41" s="15" t="inlineStr">
+        <is>
+          <t>缺陷</t>
+        </is>
+      </c>
+      <c r="E41" s="16" t="inlineStr">
+        <is>
+          <t>监控指标与侧栏用户仍为 mock（未接真实数据/两处用户不一致）</t>
+        </is>
+      </c>
+      <c r="F41" s="15" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="G41" s="22" t="inlineStr">
+        <is>
+          <t>⬜ 未开始</t>
+        </is>
+      </c>
+      <c r="H41" s="15" t="inlineStr">
+        <is>
+          <t>Claude</t>
+        </is>
+      </c>
+      <c r="I41" s="15" t="inlineStr">
+        <is>
+          <t>3.5</t>
+        </is>
+      </c>
+      <c r="J41" s="16" t="inlineStr">
+        <is>
+          <t>指标来自真实数据或标注占位；侧栏用户=登录用户全页一致</t>
+        </is>
+      </c>
+      <c r="K41" s="15" t="inlineStr">
+        <is>
+          <t>L4</t>
+        </is>
+      </c>
+      <c r="L41" s="15" t="inlineStr">
+        <is>
+          <t>未写</t>
+        </is>
+      </c>
+      <c r="M41" s="15" t="inlineStr">
+        <is>
+          <t>⬜</t>
+        </is>
+      </c>
+      <c r="N41" s="15" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O41" s="16" t="inlineStr">
+        <is>
+          <t>Issue #74</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="15" t="inlineStr">
+        <is>
+          <t>BUG-75</t>
+        </is>
+      </c>
+      <c r="B42" s="15" t="inlineStr">
+        <is>
+          <t>D2</t>
+        </is>
+      </c>
+      <c r="C42" s="15" t="inlineStr">
+        <is>
+          <t>Phase 4</t>
+        </is>
+      </c>
+      <c r="D42" s="15" t="inlineStr">
+        <is>
+          <t>缺陷</t>
+        </is>
+      </c>
+      <c r="E42" s="16" t="inlineStr">
+        <is>
+          <t>agents-admin 未消费 /api/agents 真实数据（API+隔离已就绪）</t>
+        </is>
+      </c>
+      <c r="F42" s="15" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="G42" s="22" t="inlineStr">
+        <is>
+          <t>⬜ 未开始</t>
+        </is>
+      </c>
+      <c r="H42" s="15" t="inlineStr">
+        <is>
+          <t>Claude</t>
+        </is>
+      </c>
+      <c r="I42" s="15" t="inlineStr">
+        <is>
+          <t>4.1.1</t>
+        </is>
+      </c>
+      <c r="J42" s="16" t="inlineStr">
+        <is>
+          <t>列表来自/api/agents真实数据；跨租户不可见；刷新仍在</t>
+        </is>
+      </c>
+      <c r="K42" s="15" t="inlineStr">
+        <is>
+          <t>L3</t>
+        </is>
+      </c>
+      <c r="L42" s="15" t="inlineStr">
+        <is>
+          <t>未写</t>
+        </is>
+      </c>
+      <c r="M42" s="15" t="inlineStr">
+        <is>
+          <t>⬜</t>
+        </is>
+      </c>
+      <c r="N42" s="15" t="inlineStr">
+        <is>
+          <t>S1-AGT</t>
+        </is>
+      </c>
+      <c r="O42" s="16" t="inlineStr">
+        <is>
+          <t>Issue #75｜并入4.1.1</t>
         </is>
       </c>
     </row>

--- a/docs/AIPaddle-项目进度管控.xlsx
+++ b/docs/AIPaddle-项目进度管控.xlsx
@@ -1184,7 +1184,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O42"/>
+  <dimension ref="A1:O43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -4371,6 +4371,83 @@
       <c r="O42" s="16" t="inlineStr">
         <is>
           <t>Issue #75｜并入4.1.1</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="15" t="inlineStr">
+        <is>
+          <t>D1-E</t>
+        </is>
+      </c>
+      <c r="B43" s="15" t="inlineStr">
+        <is>
+          <t>D1</t>
+        </is>
+      </c>
+      <c r="C43" s="15" t="inlineStr">
+        <is>
+          <t>Phase 0</t>
+        </is>
+      </c>
+      <c r="D43" s="15" t="inlineStr">
+        <is>
+          <t>集成</t>
+        </is>
+      </c>
+      <c r="E43" s="16" t="inlineStr">
+        <is>
+          <t>E道D1集成：合并绿灯PR+修红+部署整合（不产新功能）</t>
+        </is>
+      </c>
+      <c r="F43" s="15" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="G43" s="22" t="inlineStr">
+        <is>
+          <t>🔄 进行中</t>
+        </is>
+      </c>
+      <c r="H43" s="15" t="inlineStr">
+        <is>
+          <t>E道(Claude)</t>
+        </is>
+      </c>
+      <c r="I43" s="15" t="inlineStr">
+        <is>
+          <t>各道D1产出</t>
+        </is>
+      </c>
+      <c r="J43" s="16" t="inlineStr">
+        <is>
+          <t>待集成绿灯PR全并入main、main CI绿、线上最新可访问</t>
+        </is>
+      </c>
+      <c r="K43" s="15" t="inlineStr">
+        <is>
+          <t>L1</t>
+        </is>
+      </c>
+      <c r="L43" s="15" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M43" s="15" t="inlineStr">
+        <is>
+          <t>🔄</t>
+        </is>
+      </c>
+      <c r="N43" s="15" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O43" s="16" t="inlineStr">
+        <is>
+          <t>Issue #77</t>
         </is>
       </c>
     </row>

--- a/docs/AIPaddle-项目进度管控.xlsx
+++ b/docs/AIPaddle-项目进度管控.xlsx
@@ -21,7 +21,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="9">
+  <fonts count="10">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -74,6 +74,9 @@
       <b val="1"/>
       <color rgb="00111827"/>
       <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="9">
@@ -145,7 +148,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -213,6 +216,7 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -1184,7 +1188,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O43"/>
+  <dimension ref="A1:P59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1280,6 +1284,11 @@
           <t>备注</t>
         </is>
       </c>
+      <c r="P1" s="23" t="inlineStr">
+        <is>
+          <t>并行道</t>
+        </is>
+      </c>
     </row>
     <row r="2" ht="36" customHeight="1">
       <c r="A2" s="15" t="inlineStr">
@@ -1884,6 +1893,11 @@
           <t>Issue #55；等Secret</t>
         </is>
       </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>E道·部署</t>
+        </is>
+      </c>
     </row>
     <row r="10" ht="36" customHeight="1">
       <c r="A10" s="15" t="inlineStr">
@@ -1957,6 +1971,11 @@
         </is>
       </c>
       <c r="O10" s="16" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>E道·测试基建</t>
+        </is>
+      </c>
     </row>
     <row r="11" ht="36" customHeight="1">
       <c r="A11" s="15" t="inlineStr">
@@ -2030,6 +2049,11 @@
         </is>
       </c>
       <c r="O11" s="16" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>E道·测试基建</t>
+        </is>
+      </c>
     </row>
     <row r="12" ht="36" customHeight="1">
       <c r="A12" s="15" t="inlineStr">
@@ -2107,6 +2131,11 @@
           <t>GitHub Settings操作</t>
         </is>
       </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>E道·测试基建</t>
+        </is>
+      </c>
     </row>
     <row r="13" ht="36" customHeight="1">
       <c r="A13" s="15" t="inlineStr">
@@ -3526,6 +3555,11 @@
           <t>需先配DEPLOY_SSH_KEY</t>
         </is>
       </c>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>E道·部署</t>
+        </is>
+      </c>
     </row>
     <row r="32" ht="36" customHeight="1">
       <c r="A32" s="15" t="inlineStr">
@@ -3603,6 +3637,11 @@
           <t>35条CI绿；L5隔离专项待补</t>
         </is>
       </c>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>E道·测试</t>
+        </is>
+      </c>
     </row>
     <row r="33" ht="36" customHeight="1">
       <c r="A33" s="15" t="inlineStr">
@@ -3680,6 +3719,11 @@
           <t>Issue #62</t>
         </is>
       </c>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>B道·Agent</t>
+        </is>
+      </c>
     </row>
     <row r="34" ht="36" customHeight="1">
       <c r="A34" s="15" t="inlineStr">
@@ -3757,6 +3801,11 @@
           <t>Issue #63</t>
         </is>
       </c>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>B道·Agent</t>
+        </is>
+      </c>
     </row>
     <row r="35" ht="36" customHeight="1">
       <c r="A35" s="15" t="inlineStr">
@@ -3834,6 +3883,11 @@
           <t>Issue #64</t>
         </is>
       </c>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>B道·Agent</t>
+        </is>
+      </c>
     </row>
     <row r="36" ht="36" customHeight="1">
       <c r="A36" s="15" t="inlineStr">
@@ -3911,6 +3965,11 @@
           <t>Issue #65</t>
         </is>
       </c>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>B道·Agent</t>
+        </is>
+      </c>
     </row>
     <row r="37" ht="36" customHeight="1">
       <c r="A37" s="15" t="inlineStr">
@@ -3988,6 +4047,11 @@
           <t>Issue #66</t>
         </is>
       </c>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>B道·Agent</t>
+        </is>
+      </c>
     </row>
     <row r="38" ht="36" customHeight="1">
       <c r="A38" s="15" t="inlineStr">
@@ -4065,6 +4129,11 @@
           <t>Issue #67</t>
         </is>
       </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>B道·Agent</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="15" t="inlineStr">
@@ -4448,6 +4517,818 @@
       <c r="O43" s="16" t="inlineStr">
         <is>
           <t>Issue #77</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>4.2.1</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Phase 4</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>知识库</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>文档上传(PDF)+存储</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>Claude Code</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>2.4</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>含 migration0003 修全表软删RLS;已合并</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>A道·知识库</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>4.2.2</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Phase 4</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>知识库</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>解析/切块/向量化入库</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>⬜ 未开始</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>Claude Code</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>4.2.1</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>🔴依赖4.2.1+共享嵌入客户端(DashScope v4/1536)</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>A道·知识库</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>4.2.3</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Phase 4</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>知识库</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>RAG问答带引用(A-6)</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>⬜ 未开始</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>Claude Code</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>4.2.2</t>
+        </is>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>🔴依赖4.2.2;L5金标准评测≥80%</t>
+        </is>
+      </c>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>A道·知识库</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>4.2.4</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Phase 4</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>知识库</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>办公文件处理通道①(A-7)</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>⬜ 未开始</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>Claude Code</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>4.2.2</t>
+        </is>
+      </c>
+      <c r="O47" t="inlineStr">
+        <is>
+          <t>复用解析管线;与C5共用ADR-006</t>
+        </is>
+      </c>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>A道·知识库</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>4.3.0</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Phase 4</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>Skill</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>MCP管理中心最小版</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>⬜ 未开始</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>Claude Code</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O48" t="inlineStr">
+        <is>
+          <t>ADR-004</t>
+        </is>
+      </c>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>C道·Skill</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>4.3.1</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Phase 4</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>Skill</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>Skill CRUD+发布+MCP封装</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>⬜ 未开始</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>Claude Code</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>4.3.0</t>
+        </is>
+      </c>
+      <c r="O49" t="inlineStr">
+        <is>
+          <t>🔴完成即解锁D道4.4.2</t>
+        </is>
+      </c>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>C道·Skill</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>4.3.2</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Phase 4</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>Skill</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>Skill调用测试入口</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>⬜ 未开始</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>Claude Code</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>4.3.1</t>
+        </is>
+      </c>
+      <c r="O50" t="inlineStr"/>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>C道·Skill</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>4.3.3</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Phase 4</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>Skill</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>Skill Copilot</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>⬜ 未开始</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>Claude Code</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>4.3.1</t>
+        </is>
+      </c>
+      <c r="O51" t="inlineStr">
+        <is>
+          <t>ADR-005</t>
+        </is>
+      </c>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>C道·Skill</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>4.3.4</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Phase 4</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>Skill</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>办公云盘MCP接入通道②</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>⬜ 未开始</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>Claude Code</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>4.3.0</t>
+        </is>
+      </c>
+      <c r="O52" t="inlineStr">
+        <is>
+          <t>与A3共用ADR-006文件管线</t>
+        </is>
+      </c>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>C道·Skill</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>4.4.1</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Phase 4</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>Workflow</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>图结构校验+保存/加载</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>⬜ 未开始</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>Claude Code</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O53" t="inlineStr"/>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>D道·Workflow</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>4.4.2</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Phase 4</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>Workflow</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>节点配置+Tool只引用已发布Skill</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>⬜ 未开始</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>Claude Code</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>4.4.1,4.3.1</t>
+        </is>
+      </c>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>🔴🔴跨道硬依赖C道4.3.1(Skill发布)</t>
+        </is>
+      </c>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>D道·Workflow</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>4.4.3</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Phase 4</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>Workflow</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>最小执行引擎(2-3种节点串行)</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>⬜ 未开始</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>Claude Code</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>4.4.2</t>
+        </is>
+      </c>
+      <c r="O55" t="inlineStr"/>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>D道·Workflow</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>4.4.4</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Phase 4</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>Workflow</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>版本发布与运行历史</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>⬜ 未开始</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>Claude Code</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>4.4.3</t>
+        </is>
+      </c>
+      <c r="O56" t="inlineStr"/>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>D道·Workflow</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>4.4.5</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Phase 4</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>Workflow</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>Workflow/Chatflow Copilot</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>⬜ 未开始</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>Claude Code</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>4.4.2</t>
+        </is>
+      </c>
+      <c r="O57" t="inlineStr">
+        <is>
+          <t>ADR-005</t>
+        </is>
+      </c>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>D道·Workflow</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>4.5.1</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Phase 4</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>成员租户</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>成员邀请/编辑/禁用/角色变更</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>⬜ 未开始</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>Claude Code</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>3.4</t>
+        </is>
+      </c>
+      <c r="O58" t="inlineStr">
+        <is>
+          <t>权限矩阵已就绪</t>
+        </is>
+      </c>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>E道·成员租户</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>4.5.2</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Phase 4</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>成员租户</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>租户创建/编辑/停用+配额</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>⬜ 未开始</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>Claude Code</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>4.5.1</t>
+        </is>
+      </c>
+      <c r="O59" t="inlineStr"/>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>E道·成员租户</t>
         </is>
       </c>
     </row>

--- a/docs/AIPaddle-项目进度管控.xlsx
+++ b/docs/AIPaddle-项目进度管控.xlsx
@@ -8,10 +8,11 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="仪表盘" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="任务清单" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="里程碑关口" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="决策日志" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="问题台账" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="并行通道分工" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="任务清单" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="里程碑关口" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="决策日志" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="问题台账" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -21,7 +22,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="10">
+  <fonts count="15">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -78,8 +79,30 @@
     <font>
       <b val="1"/>
     </font>
+    <font>
+      <b val="1"/>
+      <sz val="14"/>
+    </font>
+    <font>
+      <i val="1"/>
+      <color rgb="00888888"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <sz val="12"/>
+    </font>
   </fonts>
-  <fills count="9">
+  <fills count="15">
     <fill>
       <patternFill/>
     </fill>
@@ -121,8 +144,38 @@
         <fgColor rgb="00FFFFFF"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="001F3864"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="002E75B6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00548235"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00BF8F00"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="009E480E"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="007030A0"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -144,11 +197,25 @@
         <color rgb="00CBD5E1"/>
       </bottom>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="00CCCCCC"/>
+      </left>
+      <right style="thin">
+        <color rgb="00CCCCCC"/>
+      </right>
+      <top style="thin">
+        <color rgb="00CCCCCC"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00CCCCCC"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="34">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -217,6 +284,30 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="12" fillId="9" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="10" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="11" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="12" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="13" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="14" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -1188,6 +1279,308 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:E27"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="52" customWidth="1" min="3" max="3"/>
+    <col width="34" customWidth="1" min="4" max="4"/>
+    <col width="34" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="24" t="inlineStr">
+        <is>
+          <t>AIPaddle 五通道并行执行分工（2026-07-20）</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="25" t="inlineStr">
+        <is>
+          <t>权威计划: docs/PARALLEL_EXECUTION_PLAN.md ｜ 每道=独立 git worktree+一个实例 ｜ 🔴=硬约束不完成不下一步</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="26" t="inlineStr">
+        <is>
+          <t>通道</t>
+        </is>
+      </c>
+      <c r="B4" s="26" t="inlineStr">
+        <is>
+          <t>负责模块</t>
+        </is>
+      </c>
+      <c r="C4" s="26" t="inlineStr">
+        <is>
+          <t>任务链（按序执行）</t>
+        </is>
+      </c>
+      <c r="D4" s="26" t="inlineStr">
+        <is>
+          <t>兼职/职责</t>
+        </is>
+      </c>
+      <c r="E4" s="26" t="inlineStr">
+        <is>
+          <t>关键硬约束</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="27" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="B5" s="28" t="inlineStr">
+        <is>
+          <t>知识库 / RAG</t>
+        </is>
+      </c>
+      <c r="C5" s="28" t="inlineStr">
+        <is>
+          <t>4.2.1 ✅ → 4.2.2 向量化 → 4.2.3 RAG问答 → 4.2.4 文件处理</t>
+        </is>
+      </c>
+      <c r="D5" s="28" t="inlineStr">
+        <is>
+          <t>Schema/迁移唯一 owner + 共享 lib/ai 客户端</t>
+        </is>
+      </c>
+      <c r="E5" s="28" t="inlineStr">
+        <is>
+          <t>🔴4.2.2→4.2.3 序；改表必过 A</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="29" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B6" s="28" t="inlineStr">
+        <is>
+          <t>Agent 管理</t>
+        </is>
+      </c>
+      <c r="C6" s="28" t="inlineStr">
+        <is>
+          <t>4.1.1 CRUD → 4.1.2 状态机 → 4.1.3 审核 → 4.1.4 调用 → 4.1.5 日志 → 4.1.6 Copilot</t>
+        </is>
+      </c>
+      <c r="D6" s="28" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E6" s="28" t="inlineStr">
+        <is>
+          <t>🔴道内严格串行；LLM 用 lib/ai</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="30" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="B7" s="28" t="inlineStr">
+        <is>
+          <t>Skill Hub / MCP</t>
+        </is>
+      </c>
+      <c r="C7" s="28" t="inlineStr">
+        <is>
+          <t>4.3.0 MCP中心 → 4.3.1 Skill CRUD/发布 → 4.3.2 调用测试 / 4.3.3 Copilot → 4.3.4 云盘</t>
+        </is>
+      </c>
+      <c r="D7" s="28" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E7" s="28" t="inlineStr">
+        <is>
+          <t>🔴C2(4.3.1)完成即解锁 D</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="31" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="B8" s="28" t="inlineStr">
+        <is>
+          <t>Workflow</t>
+        </is>
+      </c>
+      <c r="C8" s="28" t="inlineStr">
+        <is>
+          <t>4.4.1 图保存 → 4.4.2 节点配置 → 4.4.3 执行引擎 → 4.4.4 版本 → 4.4.5 Copilot</t>
+        </is>
+      </c>
+      <c r="D8" s="28" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E8" s="28" t="inlineStr">
+        <is>
+          <t>🔴🔴D2(4.4.2) 硬等 C2(4.3.1 Skill发布)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="32" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="B9" s="28" t="inlineStr">
+        <is>
+          <t>成员租户 + 集成</t>
+        </is>
+      </c>
+      <c r="C9" s="28" t="inlineStr">
+        <is>
+          <t>0.9 测试基建(前置) → 4.5.1 成员 → 4.5.2 租户</t>
+        </is>
+      </c>
+      <c r="D9" s="28" t="inlineStr">
+        <is>
+          <t>集成/合并 owner + 测试基建 + 部署(0.8/3.6)</t>
+        </is>
+      </c>
+      <c r="E9" s="28" t="inlineStr">
+        <is>
+          <t>🔴E0 测试基建=Gate0 前置；保 S0-ISO 绿</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="33" t="inlineStr">
+        <is>
+          <t>🔴 前置 Gate 0（开阶段4前必须全绿）</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>G0.1 4.2.1 合并 → ✅</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>G0.2 3.2~3.5 验收 → ✅（3.2 代码已修，#72 为延迟非bug）</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>G0.3 测试基建 0.9 → ⬜ 待 E 道</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>G0.4 共享 lib/ai 客户端 → ✅</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="33" t="inlineStr">
+        <is>
+          <t>🔴 跨道硬闸</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>X1 D2 硬等 C2（Workflow Tool 只引用已发布 Skill）</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>X2 A/C 共用 ADR-006 文件管线</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>X3 改表必过 A 道出迁移（禁并发改表）</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>X4 LLM/嵌入一律用 lib/ai</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>X5 🔴总硬闸: 合并前 S0-ISO 隔离必绿，红则全停</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="33" t="inlineStr">
+        <is>
+          <t>🔴 测试门（六层，测完才下一步）</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>每任务: L1 pnpm check + L2 单元 + L3 API + L6 手动验收 → 才关 Issue</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>每切片: L4 E2E + L5 专项(隔离必跑; RAG 加金标准≥80%) → 才进下一切片</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>每阶段: L6 真实用户测试</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:P59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -4873,7 +5266,6 @@
           <t>4.3.1</t>
         </is>
       </c>
-      <c r="O50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
           <t>C道·Skill</t>
@@ -5025,7 +5417,6 @@
           <t>—</t>
         </is>
       </c>
-      <c r="O53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
           <t>D道·Workflow</t>
@@ -5125,7 +5516,6 @@
           <t>4.4.2</t>
         </is>
       </c>
-      <c r="O55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
           <t>D道·Workflow</t>
@@ -5173,7 +5563,6 @@
           <t>4.4.3</t>
         </is>
       </c>
-      <c r="O56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
           <t>D道·Workflow</t>
@@ -5325,7 +5714,6 @@
           <t>4.5.1</t>
         </is>
       </c>
-      <c r="O59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
           <t>E道·成员租户</t>
@@ -5337,7 +5725,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -5583,7 +5971,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -5929,7 +6317,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>

--- a/docs/AIPaddle-项目进度管控.xlsx
+++ b/docs/AIPaddle-项目进度管控.xlsx
@@ -2243,7 +2243,7 @@
       </c>
       <c r="G9" s="11" t="inlineStr">
         <is>
-          <t>🔄 进行中</t>
+          <t>✅ 已完成</t>
         </is>
       </c>
       <c r="H9" s="15" t="inlineStr">
@@ -2283,7 +2283,7 @@
       </c>
       <c r="O9" s="16" t="inlineStr">
         <is>
-          <t>Issue #55；等Secret</t>
+          <t>Issue #55/#77 已关闭；冒烟 HTTP 200 通过（2026-07-20）</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">

--- a/docs/AIPaddle-项目进度管控.xlsx
+++ b/docs/AIPaddle-项目进度管控.xlsx
@@ -4993,7 +4993,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>⬜ 未开始</t>
+          <t>✅ 已完成</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">

--- a/docs/AIPaddle-项目进度管控.xlsx
+++ b/docs/AIPaddle-项目进度管控.xlsx
@@ -4993,7 +4993,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>⬜ 未开始</t>
+          <t>✅ 已完成</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -5045,7 +5045,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>⬜ 未开始</t>
+          <t>🔄 本地完成待合</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -5060,7 +5060,7 @@
       </c>
       <c r="O46" t="inlineStr">
         <is>
-          <t>🔴依赖4.2.2;L5金标准评测≥80%</t>
+          <t>金标准7/7=100%;feat/slice2-knowledge</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">

--- a/docs/AIPaddle-项目进度管控.xlsx
+++ b/docs/AIPaddle-项目进度管控.xlsx
@@ -5097,7 +5097,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>⬜ 未开始</t>
+          <t>🔄 本地完成待合</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">

--- a/docs/AIPaddle-项目进度管控.xlsx
+++ b/docs/AIPaddle-项目进度管控.xlsx
@@ -2129,7 +2129,7 @@
       </c>
       <c r="O7" s="16" t="inlineStr">
         <is>
-          <t>Issue #54批量建卡完成</t>
+          <t>Issue #54批量建卡完成 · 追踪迁至 docs/ISSUES.md</t>
         </is>
       </c>
     </row>
@@ -2283,7 +2283,7 @@
       </c>
       <c r="O9" s="16" t="inlineStr">
         <is>
-          <t>Issue #55/#77 已关闭；冒烟 HTTP 200 通过（2026-07-20）</t>
+          <t>Issue #55/#77 已关闭；冒烟 HTTP 200 通过（2026-07-20） · 追踪迁至 docs/ISSUES.md</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -4069,7 +4069,7 @@
       </c>
       <c r="G33" s="12" t="inlineStr">
         <is>
-          <t>⬜ 未开始</t>
+          <t>🔄 进行中</t>
         </is>
       </c>
       <c r="H33" s="15" t="inlineStr">
@@ -4109,7 +4109,7 @@
       </c>
       <c r="O33" s="16" t="inlineStr">
         <is>
-          <t>Issue #62</t>
+          <t>CRUD闭环(增删改查+8单测)待验收 · PR#5(新repo) · 追踪 docs/ISSUES.md</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
@@ -4191,7 +4191,7 @@
       </c>
       <c r="O34" s="16" t="inlineStr">
         <is>
-          <t>Issue #63</t>
+          <t>Issue #63 · 追踪迁至 docs/ISSUES.md</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
@@ -4273,7 +4273,7 @@
       </c>
       <c r="O35" s="16" t="inlineStr">
         <is>
-          <t>Issue #64</t>
+          <t>Issue #64 · 追踪迁至 docs/ISSUES.md</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
@@ -4355,7 +4355,7 @@
       </c>
       <c r="O36" s="16" t="inlineStr">
         <is>
-          <t>Issue #65</t>
+          <t>Issue #65 · 追踪迁至 docs/ISSUES.md</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
@@ -4437,7 +4437,7 @@
       </c>
       <c r="O37" s="16" t="inlineStr">
         <is>
-          <t>Issue #66</t>
+          <t>Issue #66 · 追踪迁至 docs/ISSUES.md</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
@@ -4519,7 +4519,7 @@
       </c>
       <c r="O38" s="16" t="inlineStr">
         <is>
-          <t>Issue #67</t>
+          <t>Issue #67 · 追踪迁至 docs/ISSUES.md</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
@@ -4601,7 +4601,7 @@
       </c>
       <c r="O39" s="16" t="inlineStr">
         <is>
-          <t>Issue #72｜线上验证2026-07-20</t>
+          <t>Issue #72｜线上验证2026-07-20 · 追踪迁至 docs/ISSUES.md</t>
         </is>
       </c>
     </row>
@@ -4678,7 +4678,7 @@
       </c>
       <c r="O40" s="16" t="inlineStr">
         <is>
-          <t>Issue #73｜二三级页无法使用直接原因</t>
+          <t>Issue #73｜二三级页无法使用直接原因 · 追踪迁至 docs/ISSUES.md</t>
         </is>
       </c>
     </row>
@@ -4755,7 +4755,7 @@
       </c>
       <c r="O41" s="16" t="inlineStr">
         <is>
-          <t>Issue #74</t>
+          <t>Issue #74 · 追踪迁至 docs/ISSUES.md</t>
         </is>
       </c>
     </row>
@@ -4792,7 +4792,7 @@
       </c>
       <c r="G42" s="22" t="inlineStr">
         <is>
-          <t>⬜ 未开始</t>
+          <t>✅ 已完成</t>
         </is>
       </c>
       <c r="H42" s="15" t="inlineStr">
@@ -4832,7 +4832,7 @@
       </c>
       <c r="O42" s="16" t="inlineStr">
         <is>
-          <t>Issue #75｜并入4.1.1</t>
+          <t>agents-admin 已接真实数据(b8d6d5c9)；追踪 docs/ISSUES.md</t>
         </is>
       </c>
     </row>
@@ -4909,7 +4909,7 @@
       </c>
       <c r="O43" s="16" t="inlineStr">
         <is>
-          <t>Issue #77</t>
+          <t>Issue #77 · 追踪迁至 docs/ISSUES.md</t>
         </is>
       </c>
     </row>
